--- a/packages/xlsx/tests/fixtures/result.xlsx
+++ b/packages/xlsx/tests/fixtures/result.xlsx
@@ -16,7 +16,7 @@
     <t>Name: Germán</t>
   </si>
   <si>
-    <t>Date: Mon Jan 01 2024 21:00:00 GMT-0300 (Argentina Standard Time)</t>
+    <t>Date: Tue Jan 02 2024 00:00:00 GMT+0000 (Coordinated Universal Time)</t>
   </si>
   <si>
     <t>ID: 001</t>
@@ -28,7 +28,7 @@
     <t>Price: 120.5</t>
   </si>
   <si>
-    <t>Item date: Tue Jan 02 2024 21:00:00 GMT-0300 (Argentina Standard Time)</t>
+    <t>Item date: Wed Jan 03 2024 00:00:00 GMT+0000 (Coordinated Universal Time)</t>
   </si>
   <si>
     <t>Missing: [[items.missingProp]]</t>
@@ -468,7 +468,7 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <f>B2*C2</f>
+        <f>B3*C3</f>
       </c>
     </row>
   </sheetData>
